--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260923.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260923.xlsx
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>60,628,621</t>
+          <t>36,106,442</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>36,106,442</t>
+          <t>60,628,621</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>15,474,728</t>
+          <t>7,109,640</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>7,109,640</t>
+          <t>15,474,728</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>212,995,364</t>
+          <t>4,101,274</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>4,101,274</t>
+          <t>212,995,364</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>113,479,974</t>
+          <t>7,198,300</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>7,198,300</t>
+          <t>113,479,974</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
